--- a/spec/Docs/01_Design/OrnamentDesignVersion/饰品列表.xlsx
+++ b/spec/Docs/01_Design/OrnamentDesignVersion/饰品列表.xlsx
@@ -13,8 +13,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K57"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -174,7 +174,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>根源之梦；闹钟</t>
+          <t>根源之梦；破旧闹钟</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>苹果；废弃物；梦境之种</t>
+          <t>苹果；废弃物；空心果壳</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -475,12 +475,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>捕梦到占格数大于等于4的物品时：本次梦值消耗-2，最低为1。</t>
+          <t>捕梦到占格数大于等于4的可抽取物品时：本次梦值消耗-2，最低为1。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>礼物盒；大型污染物；大型梦种组件</t>
+          <t>礼物盒；大型污染物；中央引擎；月冠温床</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>梦境之种/播种</t>
+          <t>梦之种/播种</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>梦境之种/成长</t>
+          <t>梦之种/成长</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>梦境之种/丢弃</t>
+          <t>梦之种/丢弃</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>食物/梦境之种</t>
+          <t>食物/梦之种</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>食物被丢弃时：+4分，并向随机空格播种。</t>
+          <t>苹果或美味烧鸡被丢弃时：+4分，并向随机空格播种。</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1439,22 +1439,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>梦境之种/成长</t>
+          <t>梦之种/成长</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>梦境之种等级提升时：+2分。若提升到3级或以上，额外+4分。</t>
+          <t>梦境之种等级提升时：+1分。若因此达到10、20或30级，额外+8分。</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>月露瓶；堆肥袋</t>
+          <t>月露瓶；堆肥袋；温室灯</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>奖励持续培养，而不是只生成。</t>
+          <t>奖励持续培养，并把变大节点做成明确反馈。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>梦境之种/撞击</t>
+          <t>梦之种/撞击</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>梦境之种/空间</t>
+          <t>梦之种/空间</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>播种失败时：+8分，每次捕梦后限1次。</t>
+          <t>播种没有生成或升级梦境之种时，或梦境之种因变大空间不足掉出背包时：+8分。每次捕梦后限1次。</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>避免满背包导致播种完全亏损。</t>
+          <t>避免满背包或成长失败导致梦种路线完全亏损。</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>食物/梦境之种</t>
+          <t>食物/梦之种</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>梦境之种/收获</t>
+          <t>梦之种/收获</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>每个局内关卡第一次有4级或以上梦境之种结算：+20分。</t>
+          <t>每个局内关卡第一次有4x4梦境之种完成结算：+25分。</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>高等级梦种；温室玻璃</t>
+          <t>高等级梦种；温室玻璃；月冠温床</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>梦境之种/回复</t>
+          <t>梦之种/回复</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>梦境之种升级到5级时：+3梦值，每个局内关卡限1次。</t>
+          <t>梦境之种达到30级或变为4x4时：+3梦值，每个局内关卡限1次。</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>纵向培育；月露瓶</t>
+          <t>纵向培育；月露瓶；温室灯</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>机械物品成功传导撞击时：+2分，每条链最多触发5次。</t>
+          <t>机械物品成功传导撞击或曲线传动命中机械物品时：+2分，每条链最多触发5次。</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>机械长链；链长计数器</t>
+          <t>机械长链；链长计数器；顺转弯管</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>每个局内关卡第一次撞击链停止时，若最后被撞物品是机械：从该物品反方向撞击！</t>
+          <t>每个局内关卡第一次撞击链停止时，若最后被撞物品是机械：从该物品反方向发起一次机械撞击！</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>每条链第一次命中机械物品时：该物品本次可以向相邻同方向物品与任意1个相邻物品各传导一次。</t>
+          <t>每条链第一次命中机械物品时：该物品本次触发双向传动！每条链限1次。</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>万向齿轮式构筑；长链</t>
+          <t>双轴转轮；曲线传动；长链</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>链结束：若本次命中大于等于8个物品，+25分；若大于等于12个物品，改为+45分。</t>
+          <t>链结束：若本次链机械命中数大于等于8，+25分；若大于等于12，改为+45分。</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>机械高阶长链</t>
+          <t>机械高阶长链；中央引擎；计数轮</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2633,6 +2633,312 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>透明奖杯</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>工具腰包</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>55</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>通用/道具</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>每个局内关卡第一次使用道具：+4分。每使用3个道具：+6分，每个局内关卡限1次。</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>小补丁；梦值糖；破弹珠</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>给道具系统一个低风险基础收益。</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>缝着小口袋的腰包</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>标本针盒</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>80</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>污染/道具</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>使用道具为物品添加污染或净化污染时：+4分。若目标是废弃物，额外+2分。每次捕梦后最多触发2次。</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>黑墨水；消毒喷雾；腐蚀酸</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>让污染道具成为启动和净化之间的桥接。</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>针盒和黑色样本</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>园艺工具包</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>梦境之种与丢弃</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>85</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>梦之种/道具</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>使用道具播种或使梦境之种升级时：+4分；若因此使梦境之种变大，额外+10分。</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>小水滴；肥料包；快速发芽剂</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>支持梦种道具爆发，但收益绑定成长节点。</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>园艺剪和小铲组成的工具包</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>回收挂钩</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>梦境之种与丢弃</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <v>90</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>丢弃/道具</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>使用道具到丢弃区，或使用道具使下一次丢弃获得额外收益时：+6分；若本次丢弃的是废弃物，额外+1梦值。每个局内关卡最多+2梦值。</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>回收夹；苹果蜡；废弃物</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>把一次性道具和丢弃路线连接起来。</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>金属回收钩</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>校准螺丝刀</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>机械与撞击</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>85</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>机械/道具</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>使用道具到机械物品上时：该物品本局内下一次成功传导或曲线传动命中机械物品时+6分。每次捕梦后限1次。</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>转向螺丝；破弹珠；传动油</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>鼓励用道具主动修正机械链。</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>带刻度的小螺丝刀</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>万用工具箱</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>后期混合</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="E57">
+        <v>4</v>
+      </c>
+      <c r="F57">
+        <v>145</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>混合/道具</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>每个局内关卡第一次分别使用到物品、空格和捕梦区的道具时，各记录1种目标类型；记录达到3种时：+30分，并获得1个随机普通道具。每局限1次。</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>多目标道具；梦境钥匙；小水滴</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>鼓励多类型道具使用，而不是只堆单一强道具。</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>装满旧工具的木箱</t>
         </is>
       </c>
     </row>
@@ -2642,8 +2948,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K12"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2803,7 +3109,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>根源之梦；闹钟</t>
+          <t>根源之梦；破旧闹钟</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3007,7 +3313,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>苹果；废弃物；梦境之种</t>
+          <t>苹果；废弃物；空心果壳</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3104,12 +3410,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>捕梦到占格数大于等于4的物品时：本次梦值消耗-2，最低为1。</t>
+          <t>捕梦到占格数大于等于4的可抽取物品时：本次梦值消耗-2，最低为1。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>礼物盒；大型污染物；大型梦种组件</t>
+          <t>礼物盒；大型污染物；中央引擎；月冠温床</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3222,6 +3528,57 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>羽毛形吊坠</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>51</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>工具腰包</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>55</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>通用/道具</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>每个局内关卡第一次使用道具：+4分。每使用3个道具：+6分，每个局内关卡限1次。</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>小补丁；梦值糖；破弹珠</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>给道具系统一个低风险基础收益。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>缝着小口袋的腰包</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3588,749 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K14"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="62" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>饰品</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>稀有度</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>最早出现层</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>推荐价格</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>主要联动</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>设计目的</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>视觉效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>防护手套</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>污染/防护</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>每个局内关卡前2次污染物品结算：+2分。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>纸团；漏水钢笔</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>缓解污染前期收益低的问题。</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>橡胶手套</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>12</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>密封瓶</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>55</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>污染/叠层</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>每个局内关卡第一次有物品获得污染：+4分。</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>所有叠污染物品</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>让第一次叠污染有即时反馈。</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>塞紧的玻璃瓶</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>13</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>活性培养皿</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>65</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>污染/叠层</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>已经有污染的物品再次获得污染时：+2分，每次捕梦后最多触发3次。</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>小药瓶；过期药物；针管</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>奖励持续叠同一批污染目标。</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>发光培养皿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>14</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>漏液阀</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>85</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>污染/撞击</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>根源之梦命中物品后：该物品+1污染。</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>根源之梦；密封瓶；活性培养皿</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>把底层撞击源转化为污染启动。</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>滴着黑水的阀门</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>15</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>污斑贴纸</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>60</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>污染/废弃物</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>捕梦到废弃物：随机1个废弃物+1污染。</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>纸团；joker；废弃物池</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>让废弃物不只是负担。</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>黑色污点贴纸</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>16</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>废物收据</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>75</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>污染/废弃物</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>废弃物完成结算后：若其有污染，+其污染层数分。每个物品每条链限1次。</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>纸团；伤心泰迪熊；针管</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>给废弃物污染路线提供基础出口，避免被污染复制。</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>发黄收据</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>17</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>腐蚀指南</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>90</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>污染/结算</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>污染额外触发的收益效果：每次额外+1分。</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>所有污染结算</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>放大污染层，但幅度控制在小额线性。</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>边角被腐蚀的书</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>18</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>净化铃</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>90</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>污染/净化</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>每净化1层污染：+1梦值，每个局内关卡最多+5梦值。</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>垃圾袋；垃圾回收器；净化分支</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>给污染流提供少量回复出口。</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>透明小铃铛</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>19</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>黑色雨衣</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>85</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>污染/防护</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>污染层数大于等于3的物品完成结算后：+5分。每个物品每条链限1次。</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>过期药物；针管</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>奖励高层污染，但不随污染复制。</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>黑色雨衣</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>20</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>病理镜</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>125</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>污染/结算</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>污染层数大于等于5的物品完成结算后：+污染层数x2分。每个物品每条链限1次。</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>过期药物；伤心泰迪熊；黑潮瓶</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>高层污染的稀有增幅，但不直接翻倍终端。</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>显微镜镜片</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>21</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>黑潮瓶</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>145</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>污染/叠层</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>每捕梦6次：所有已经有污染的物品+1污染。</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>密封瓶；活性培养皿；病理镜</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>提供后期污染群体成长，但降低频率。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>装着黑潮的瓶子</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>22</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>黑市垃圾袋</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>140</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>污染/净化/废弃物</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>每净化3层污染：+8分。若被净化物品是废弃物，额外+1梦值。</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>垃圾袋；净化铃；垃圾回收器</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>作为污染净化分支的收益出口。</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>贴着价格标签的垃圾袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>52</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>标本针盒</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>80</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>污染/道具</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>使用道具为物品添加污染或净化污染时：+4分。若目标是废弃物，额外+2分。每次捕梦后最多触发2次。</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>黑墨水；消毒喷雾；腐蚀酸</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>让污染道具成为启动和净化之间的桥接。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>针盒和黑色样本</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:K13"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3306,16 +4405,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>防护手套</t>
+          <t>园丁手套</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3331,42 +4430,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>污染/防护</t>
+          <t>梦之种/播种</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>每个局内关卡前2次污染物品结算：+2分。</t>
+          <t>每个局内关卡第一次播种：额外+3分。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>纸团；漏水钢笔</t>
+          <t>播种物品；梦境之种</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>缓解污染前期收益低的问题。</t>
+          <t>让播种有即时收益。</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>橡胶手套</t>
+          <t>土黄色园艺手套</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>密封瓶</t>
+          <t>月露瓶</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3375,100 +4474,100 @@
         </is>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>污染/叠层</t>
+          <t>梦之种/成长</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>每个局内关卡第一次有物品获得污染：+4分。</t>
+          <t>每捕梦4次：随机1个梦境之种等级+1。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>所有叠污染物品</t>
+          <t>播种路线；根源之梦节奏</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>让第一次叠污染有即时反馈。</t>
+          <t>提供稳定成长来源。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>塞紧的玻璃瓶</t>
+          <t>装着月露的小瓶</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>活性培养皿</t>
+          <t>堆肥袋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>进阶</t>
         </is>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>污染/叠层</t>
+          <t>梦之种/丢弃</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>已经有污染的物品再次获得污染时：+2分，每次捕梦后最多触发3次。</t>
+          <t>每丢弃1个物品：随机1个梦境之种等级+1，每次捕梦后最多触发2次。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>小药瓶；过期药物；针管</t>
+          <t>苹果；废弃物；梦境之种</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>奖励持续叠同一批污染目标。</t>
+          <t>把丢弃转成梦种成长。</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>发光培养皿</t>
+          <t>小堆肥袋</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>漏液阀</t>
+          <t>蜂蜜勺</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3480,97 +4579,97 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>污染/撞击</t>
+          <t>食物/梦之种</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>根源之梦命中物品后：该物品+1污染。</t>
+          <t>苹果或美味烧鸡被丢弃时：+4分，并向随机空格播种。</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>根源之梦；密封瓶；活性培养皿</t>
+          <t>苹果；美味烧鸡；播种</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>把底层撞击源转化为污染启动。</t>
+          <t>强化食物与播种的桥接。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>滴着黑水的阀门</t>
+          <t>沾蜂蜜的木勺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>污斑贴纸</t>
+          <t>温室玻璃</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>进阶</t>
         </is>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>污染/废弃物</t>
+          <t>梦之种/成长</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>捕梦到废弃物：随机1个废弃物+1污染。</t>
+          <t>梦境之种等级提升时：+1分。若因此达到10、20或30级，额外+8分。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>纸团；joker；废弃物池</t>
+          <t>月露瓶；堆肥袋；温室灯</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>让废弃物不只是负担。</t>
+          <t>奖励持续培养，并把变大节点做成明确反馈。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>黑色污点贴纸</t>
+          <t>透明温室玻璃片</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>废物收据</t>
+          <t>根须铃</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3579,49 +4678,49 @@
         </is>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>污染/废弃物</t>
+          <t>梦之种/撞击</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>废弃物完成结算后：若其有污染，+其污染层数分。每个物品每条链限1次。</t>
+          <t>梦境之种被撞后：相邻1个梦境之种等级+1。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>纸团；伤心泰迪熊；针管</t>
+          <t>根源之梦；梦种密集摆放</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>给废弃物污染路线提供基础出口，避免被污染复制。</t>
+          <t>鼓励梦种之间靠近形成网络。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>发黄收据</t>
+          <t>缠着根须的小铃</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>腐蚀指南</t>
+          <t>种子保险</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3633,46 +4732,46 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>污染/结算</t>
+          <t>梦之种/空间</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>污染额外触发的收益效果：每次额外+1分。</t>
+          <t>播种没有生成或升级梦境之种时，或梦境之种因变大空间不足掉出背包时：+8分。每次捕梦后限1次。</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>所有污染结算</t>
+          <t>背包拥挤；大型梦种</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>放大污染层，但幅度控制在小额线性。</t>
+          <t>避免满背包或成长失败导致梦种路线完全亏损。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>边角被腐蚀的书</t>
+          <t>种子形保险牌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>净化铃</t>
+          <t>苹果木牌</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3688,93 +4787,93 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>污染/净化</t>
+          <t>食物/梦之种</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>每净化1层污染：+1梦值，每个局内关卡最多+5梦值。</t>
+          <t>苹果从背包中丢弃时：除原有效果外，额外播种1次。苹果核变回苹果时：+4分。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>垃圾袋；垃圾回收器；净化分支</t>
+          <t>苹果；苹果核；播种</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>给污染流提供少量回复出口。</t>
+          <t>把现有苹果体系接入梦种流。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>透明小铃铛</t>
+          <t>刻着苹果的木牌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>黑色雨衣</t>
+          <t>收获篮</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>进阶</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>污染/防护</t>
+          <t>梦之种/收获</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>污染层数大于等于3的物品完成结算后：+5分。每个物品每条链限1次。</t>
+          <t>每个局内关卡第一次有4x4梦境之种完成结算：+25分。</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>过期药物；针管</t>
+          <t>高等级梦种；温室玻璃；月冠温床</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>奖励高层污染，但不随污染复制。</t>
+          <t>给大型梦种提供明显终端。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>黑色雨衣</t>
+          <t>编织果篮</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>病理镜</t>
+          <t>返青符</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3790,140 +4889,140 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>污染/结算</t>
+          <t>梦之种/回复</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>污染层数大于等于5的物品完成结算后：+污染层数x2分。每个物品每条链限1次。</t>
+          <t>梦境之种达到30级或变为4x4时：+3梦值，每个局内关卡限1次。</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>过期药物；伤心泰迪熊；黑潮瓶</t>
+          <t>纵向培育；月露瓶；温室灯</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>高层污染的稀有增幅，但不直接翻倍终端。</t>
+          <t>支持高等级梦种的续航。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>显微镜镜片</t>
+          <t>绿色符纸</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>黑潮瓶</t>
+          <t>园艺工具包</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>进阶</t>
         </is>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>污染/叠层</t>
+          <t>梦之种/道具</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>每捕梦6次：所有已经有污染的物品+1污染。</t>
+          <t>使用道具播种或使梦境之种升级时：+4分；若因此使梦境之种变大，额外+10分。</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>密封瓶；活性培养皿；病理镜</t>
+          <t>小水滴；肥料包；快速发芽剂</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>提供后期污染群体成长，但降低频率。</t>
+          <t>支持梦种道具爆发，但收益绑定成长节点。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>装着黑潮的瓶子</t>
+          <t>园艺剪和小铲组成的工具包</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>黑市垃圾袋</t>
+          <t>回收挂钩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>梦境之种与丢弃</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>进阶</t>
         </is>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>污染/净化/废弃物</t>
+          <t>丢弃/道具</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>每净化3层污染：+8分。若被净化物品是废弃物，额外+1梦值。</t>
+          <t>使用道具到丢弃区，或使用道具使下一次丢弃获得额外收益时：+6分；若本次丢弃的是废弃物，额外+1梦值。每个局内关卡最多+2梦值。</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>垃圾袋；净化铃；垃圾回收器</t>
+          <t>回收夹；苹果蜡；废弃物</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>作为污染净化分支的收益出口。</t>
+          <t>把一次性道具和丢弃路线连接起来。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>贴着价格标签的垃圾袋</t>
+          <t>金属回收钩</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K11"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K12"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3997,16 +5096,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>园丁手套</t>
+          <t>弹珠发条</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4022,42 +5121,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>梦境之种/播种</t>
+          <t>机械/撞击</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>每个局内关卡第一次播种：额外+3分。</t>
+          <t>根源之梦发起撞击时：+3分。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>播种物品；梦境之种</t>
+          <t>根源之梦；导向罗盘</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>让播种有即时收益。</t>
+          <t>强化初始撞击源的基础收益。</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>土黄色园艺手套</t>
+          <t>小发条</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>月露瓶</t>
+          <t>追尾火花</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4073,42 +5172,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>梦境之种/成长</t>
+          <t>机械/撞击链</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>每捕梦4次：随机1个梦境之种等级+1。</t>
+          <t>撞击链命中大于等于3个物品时：链结束+8分。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>播种路线；根源之梦节奏</t>
+          <t>棒球；机械传导</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>提供稳定成长来源。</t>
+          <t>鼓励玩家做长链。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>装着月露的小瓶</t>
+          <t>小火花吊坠</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>堆肥袋</t>
+          <t>归位尺</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4120,46 +5219,46 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>梦境之种/丢弃</t>
+          <t>机械/摆放</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>每丢弃1个物品：随机1个梦境之种等级+1，每次捕梦后最多触发2次。</t>
+          <t>每条撞击链中，第一个被撞物品如果方向与撞击来源相同：+5分。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>苹果；废弃物；梦境之种</t>
+          <t>同方向传导；卡扣指南</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>把丢弃转成梦种成长。</t>
+          <t>奖励正确对齐。</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>小堆肥袋</t>
+          <t>带刻度的短尺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>蜂蜜勺</t>
+          <t>链长计数器</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4168,49 +5267,49 @@
         </is>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>食物/梦境之种</t>
+          <t>机械/撞击链</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>食物被丢弃时：+4分，并向随机空格播种。</t>
+          <t>链结束：+本次命中物品数量分。若命中大于等于6，额外+8分。</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>苹果；美味烧鸡；播种</t>
+          <t>追尾火花；机械流</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>强化食物与播种的桥接。</t>
+          <t>把链长直接转化为收益。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>沾蜂蜜的木勺</t>
+          <t>机械计数器</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>温室玻璃</t>
+          <t>磁性挂坠</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4222,46 +5321,46 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>梦境之种/成长</t>
+          <t>机械</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>梦境之种等级提升时：+2分。若提升到3级或以上，额外+4分。</t>
+          <t>每条撞击链第一次命中机械物品：+6分。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>月露瓶；堆肥袋</t>
+          <t>机械物品；根源之梦</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>奖励持续培养，而不是只生成。</t>
+          <t>让机械标签成为构筑信号。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>透明温室玻璃片</t>
+          <t>磁铁挂坠</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>根须铃</t>
+          <t>齿轮油</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4273,148 +5372,148 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>梦境之种/撞击</t>
+          <t>机械/传导</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>梦境之种被撞后：相邻1个梦境之种等级+1。</t>
+          <t>机械物品成功传导撞击或曲线传动命中机械物品时：+2分，每条链最多触发5次。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>根源之梦；梦种密集摆放</t>
+          <t>机械长链；链长计数器；顺转弯管</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>鼓励梦种之间靠近形成网络。</t>
+          <t>奖励机械链持续传导。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>缠着根须的小铃</t>
+          <t>小油壶</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>种子保险</t>
+          <t>反冲片</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>进阶</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>梦境之种/空间</t>
+          <t>机械/撞击</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>播种失败时：+8分，每次捕梦后限1次。</t>
+          <t>每个局内关卡第一次撞击链停止时，若最后被撞物品是机械：从该物品反方向发起一次机械撞击！</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>背包拥挤；大型梦种</t>
+          <t>机械链；终端压力表</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>避免满背包导致播种完全亏损。</t>
+          <t>给机械链提供一次补偿性延伸。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>种子形保险牌</t>
+          <t>弹性金属片</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>苹果木牌</t>
+          <t>万向轴承</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>进阶</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>食物/梦境之种</t>
+          <t>机械/传导</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>苹果从背包中丢弃时：除原有效果外，额外播种1次。苹果核变回苹果时：+4分。</t>
+          <t>每条链第一次命中机械物品时：该物品本次触发双向传动！每条链限1次。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>苹果；苹果核；播种</t>
+          <t>双轴转轮；曲线传动；长链</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>把现有苹果体系接入梦种流。</t>
+          <t>提供稀有级分叉能力。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>刻着苹果的木牌</t>
+          <t>万向轴承</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>收获篮</t>
+          <t>过载灯</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4426,46 +5525,46 @@
         <v>4</v>
       </c>
       <c r="F10">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>梦境之种/收获</t>
+          <t>机械/风险</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>每个局内关卡第一次有4级或以上梦境之种结算：+20分。</t>
+          <t>连续2次捕梦都发生过撞击时：+12分；若其中一次命中大于等于5个物品，额外+8分。</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>高等级梦种；温室玻璃</t>
+          <t>根源之梦；棒球；机械链</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>给大型梦种提供明显终端。</t>
+          <t>奖励稳定触发撞击的构筑。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>编织果篮</t>
+          <t>红色警示灯</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>返青符</t>
+          <t>终端压力表</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>梦境之种与丢弃</t>
+          <t>机械与撞击</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4477,31 +5576,82 @@
         <v>4</v>
       </c>
       <c r="F11">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>梦境之种/回复</t>
+          <t>机械/高阶</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>梦境之种升级到5级时：+3梦值，每个局内关卡限1次。</t>
+          <t>链结束：若本次链机械命中数大于等于8，+25分；若大于等于12，改为+45分。</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>纵向培育；月露瓶</t>
+          <t>机械高阶长链；中央引擎；计数轮</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>支持高等级梦种的续航。</t>
+          <t>机械流高阶奖励，从第4层开始可构筑。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>绿色符纸</t>
+          <t>大型压力表</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>55</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>校准螺丝刀</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>机械与撞击</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>进阶</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>85</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>机械/道具</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>使用道具到机械物品上时：该物品本局内下一次成功传导或曲线传动命中机械物品时+6分。每次捕梦后限1次。</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>转向螺丝；破弹珠；传动油</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>鼓励用道具主动修正机械链。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>带刻度的小螺丝刀</t>
         </is>
       </c>
     </row>
@@ -4510,9 +5660,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K10"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4586,595 +5736,6 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>弹珠发条</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>50</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>机械/撞击</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>根源之梦发起撞击时：+3分。</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>根源之梦；导向罗盘</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>强化初始撞击源的基础收益。</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>小发条</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>34</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>追尾火花</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>65</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>机械/撞击链</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>撞击链命中大于等于3个物品时：链结束+8分。</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>棒球；机械传导</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>鼓励玩家做长链。</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>小火花吊坠</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>35</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>归位尺</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>进阶</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>75</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>机械/摆放</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>每条撞击链中，第一个被撞物品如果方向与撞击来源相同：+5分。</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>同方向传导；卡扣指南</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>奖励正确对齐。</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>带刻度的短尺</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>36</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>链长计数器</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>进阶</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>90</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>机械/撞击链</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>链结束：+本次命中物品数量分。若命中大于等于6，额外+8分。</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>追尾火花；机械流</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>把链长直接转化为收益。</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>机械计数器</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>37</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>磁性挂坠</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>进阶</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>85</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>机械</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>每条撞击链第一次命中机械物品：+6分。</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>机械物品；根源之梦</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>让机械标签成为构筑信号。</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>磁铁挂坠</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>38</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>齿轮油</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>进阶</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>90</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>机械/传导</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>机械物品成功传导撞击时：+2分，每条链最多触发5次。</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>机械长链；链长计数器</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>奖励机械链持续传导。</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>小油壶</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>39</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>反冲片</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-      <c r="F8">
-        <v>120</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>机械/撞击</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>每个局内关卡第一次撞击链停止时，若最后被撞物品是机械：从该物品反方向撞击！</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>机械链；终端压力表</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>给机械链提供一次补偿性延伸。</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>弹性金属片</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>40</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>万向轴承</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>130</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>机械/传导</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>每条链第一次命中机械物品时：该物品本次可以向相邻同方向物品与任意1个相邻物品各传导一次。</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>万向齿轮式构筑；长链</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>提供稀有级分叉能力。</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>万向轴承</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>41</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>过载灯</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-      <c r="F10">
-        <v>135</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>机械/风险</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>连续2次捕梦都发生过撞击时：+12分；若其中一次命中大于等于5个物品，额外+8分。</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>根源之梦；棒球；机械链</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>奖励稳定触发撞击的构筑。</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>红色警示灯</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>42</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>终端压力表</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>机械与撞击</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>160</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>机械/高阶</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>链结束：若本次命中大于等于8个物品，+25分；若大于等于12个物品，改为+45分。</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>机械高阶长链</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>机械流高阶奖励，从第4层开始可构筑。</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>大型压力表</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K11"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="62" customWidth="1"/>
-    <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>饰品</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>稀有度</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>最早出现层</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>推荐价格</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>标签</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>效果</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>主要联动</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>设计目的</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>视觉效果</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
         <v>43</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -5578,6 +6139,57 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>透明奖杯</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>56</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>万用工具箱</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>后期混合</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>145</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>混合/道具</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>每个局内关卡第一次分别使用到物品、空格和捕梦区的道具时，各记录1种目标类型；记录达到3种时：+30分，并获得1个随机普通道具。每局限1次。</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>多目标道具；梦境钥匙；小水滴</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>鼓励多类型道具使用，而不是只堆单一强道具。</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>装满旧工具的木箱</t>
         </is>
       </c>
     </row>

--- a/spec/Docs/01_Design/OrnamentDesignVersion/饰品列表.xlsx
+++ b/spec/Docs/01_Design/OrnamentDesignVersion/饰品列表.xlsx
@@ -220,12 +220,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>每条撞击链第一次命中物品：+2分。</t>
+          <t>每次撞击结算第一次命中物品：+2分。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>根源之梦；棒球；机械链</t>
+          <t>根源之梦；棒球；机械传动</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -327,7 +327,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>高San物品；特殊物品</t>
+          <t>高梦值消耗物品；特殊物品</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>机械链；长条物品</t>
+          <t>机械传动；长条物品</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>废弃物完成结算后：若其有污染，+其污染层数分。每个物品每条链限1次。</t>
+          <t>废弃物完成结算后：若其有污染，+其污染层数分。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>污染层数大于等于3的物品完成结算后：+5分。每个物品每条链限1次。</t>
+          <t>污染层数大于等于3的物品完成结算后：+5分。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>污染层数大于等于5的物品完成结算后：+污染层数x2分。每个物品每条链限1次。</t>
+          <t>污染层数大于等于5的物品完成结算后：+污染层数x2分。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>机械/撞击链</t>
+          <t>机械/撞击结算</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>撞击链命中大于等于3个物品时：链结束+8分。</t>
+          <t>本次撞击结算命中大于等于3个物品时：在本次撞击结算全部停止后+8分。</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>鼓励玩家做长链。</t>
+          <t>鼓励玩家做长路径。</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>每条撞击链中，第一个被撞物品如果方向与撞击来源相同：+5分。</t>
+          <t>每次撞击结算中，第一个被撞物品如果方向与撞击来源相同：+5分。</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>链长计数器</t>
+          <t>命中计数器</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>机械/撞击链</t>
+          <t>机械/撞击结算</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>链结束：+本次命中物品数量分。若命中大于等于6，额外+8分。</t>
+          <t>本次撞击结算全部停止后：+本次命中物品数分。若命中大于等于6，额外+8分。</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>把链长直接转化为收益。</t>
+          <t>把命中数直接转化为收益。</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>每条撞击链第一次命中机械物品：+6分。</t>
+          <t>每次撞击结算第一次命中机械物品：+6分。</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>机械物品成功传导撞击或曲线传动命中机械物品时：+2分，每条链最多触发5次。</t>
+          <t>机械物品成功传导撞击或曲线传动命中机械物品时：+2分，每次撞击结算最多触发5次。</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>机械长链；链长计数器；顺转弯管</t>
+          <t>机械长路径；命中计数器；左传动弯管</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>奖励机械链持续传导。</t>
+          <t>奖励机械传动持续传导。</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2056,17 +2056,17 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>每个局内关卡第一次撞击链停止时，若最后被撞物品是机械：从该物品反方向发起一次机械撞击！</t>
+          <t>每个局内关卡第一次满足以下条件时触发：一次撞击结算全部停止后，最后被撞物品是机械。效果：从该物品反方向发起一次机械撞击！</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>机械链；终端压力表</t>
+          <t>机械传动；终端压力表</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>给机械链提供一次补偿性延伸。</t>
+          <t>给机械传动提供一次补偿性延伸。</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>每条链第一次命中机械物品时：该物品本次触发双向传动！每条链限1次。</t>
+          <t>每次撞击结算第一次命中机械物品时：该物品本次触发双向传动！每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>双轴转轮；曲线传动；长链</t>
+          <t>双轴转轮；曲线传动；长路径</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>根源之梦；棒球；机械链</t>
+          <t>根源之梦；棒球；机械传动</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>链结束：若本次链机械命中数大于等于8，+25分；若大于等于12，改为+45分。</t>
+          <t>本次撞击结算全部停止后：若本次命中机械物品数大于等于8，+25分；若大于等于12，改为+45分。</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>机械高阶长链；中央引擎；计数轮</t>
+          <t>机械高阶长路径；中央引擎；计数轮</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>每条撞击链命中3种或以上不同标签的物品：+15分。</t>
+          <t>每次撞击结算命中3种或以上不同标签的物品：+15分。</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>负价值物品完成结算后：额外+其负价值绝对值一半的分数，向下取整。每个物品每条链限1次。</t>
+          <t>负价值物品完成结算后：额外+其负价值绝对值一半的分数，向下取整。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>相邻两个同标签物品中，一个被撞时：另一个+2分，每条链每个物品限1次。</t>
+          <t>相邻两个同标签物品中，一个被撞时：另一个+2分，每次撞击结算每个物品限1次。</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>链结束时，若本局已经发生过污染结算、播种和大于等于5命中的撞击链：+45分，每局限1次。</t>
+          <t>本次撞击结算全部停止后时，若本局已经发生过污染结算、播种和大于等于5命中的撞击结算：+45分，每局限1次。</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>黑墨水；消毒喷雾；腐蚀酸</t>
+          <t>黑墨滴；消毒喷雾；腐蚀酸</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>鼓励用道具主动修正机械链。</t>
+          <t>鼓励用道具主动修正机械传动。</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>多目标道具；梦境钥匙；小水滴</t>
+          <t>多目标道具；梦值糖；小水滴</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>每条撞击链第一次命中物品：+2分。</t>
+          <t>每次撞击结算第一次命中物品：+2分。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>根源之梦；棒球；机械链</t>
+          <t>根源之梦；棒球；机械传动</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>高San物品；特殊物品</t>
+          <t>高梦值消耗物品；特殊物品</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>机械链；长条物品</t>
+          <t>机械传动；长条物品</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>废弃物完成结算后：若其有污染，+其污染层数分。每个物品每条链限1次。</t>
+          <t>废弃物完成结算后：若其有污染，+其污染层数分。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>污染层数大于等于3的物品完成结算后：+5分。每个物品每条链限1次。</t>
+          <t>污染层数大于等于3的物品完成结算后：+5分。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>污染层数大于等于5的物品完成结算后：+污染层数x2分。每个物品每条链限1次。</t>
+          <t>污染层数大于等于5的物品完成结算后：+污染层数x2分。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>黑墨水；消毒喷雾；腐蚀酸</t>
+          <t>黑墨滴；消毒喷雾；腐蚀酸</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>机械/撞击链</t>
+          <t>机械/撞击结算</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>撞击链命中大于等于3个物品时：链结束+8分。</t>
+          <t>本次撞击结算命中大于等于3个物品时：在本次撞击结算全部停止后+8分。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>鼓励玩家做长链。</t>
+          <t>鼓励玩家做长路径。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>每条撞击链中，第一个被撞物品如果方向与撞击来源相同：+5分。</t>
+          <t>每次撞击结算中，第一个被撞物品如果方向与撞击来源相同：+5分。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>链长计数器</t>
+          <t>命中计数器</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>机械/撞击链</t>
+          <t>机械/撞击结算</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>链结束：+本次命中物品数量分。若命中大于等于6，额外+8分。</t>
+          <t>本次撞击结算全部停止后：+本次命中物品数分。若命中大于等于6，额外+8分。</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>把链长直接转化为收益。</t>
+          <t>把命中数直接转化为收益。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>每条撞击链第一次命中机械物品：+6分。</t>
+          <t>每次撞击结算第一次命中机械物品：+6分。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5381,17 +5381,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>机械物品成功传导撞击或曲线传动命中机械物品时：+2分，每条链最多触发5次。</t>
+          <t>机械物品成功传导撞击或曲线传动命中机械物品时：+2分，每次撞击结算最多触发5次。</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>机械长链；链长计数器；顺转弯管</t>
+          <t>机械长路径；命中计数器；左传动弯管</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>奖励机械链持续传导。</t>
+          <t>奖励机械传动持续传导。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>每个局内关卡第一次撞击链停止时，若最后被撞物品是机械：从该物品反方向发起一次机械撞击！</t>
+          <t>每个局内关卡第一次满足以下条件时触发：一次撞击结算全部停止后，最后被撞物品是机械。效果：从该物品反方向发起一次机械撞击！</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>机械链；终端压力表</t>
+          <t>机械传动；终端压力表</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>给机械链提供一次补偿性延伸。</t>
+          <t>给机械传动提供一次补偿性延伸。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>每条链第一次命中机械物品时：该物品本次触发双向传动！每条链限1次。</t>
+          <t>每次撞击结算第一次命中机械物品时：该物品本次触发双向传动！每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>双轴转轮；曲线传动；长链</t>
+          <t>双轴转轮；曲线传动；长路径</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>根源之梦；棒球；机械链</t>
+          <t>根源之梦；棒球；机械传动</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>链结束：若本次链机械命中数大于等于8，+25分；若大于等于12，改为+45分。</t>
+          <t>本次撞击结算全部停止后：若本次命中机械物品数大于等于8，+25分；若大于等于12，改为+45分。</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>机械高阶长链；中央引擎；计数轮</t>
+          <t>机械高阶长路径；中央引擎；计数轮</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>鼓励用道具主动修正机械链。</t>
+          <t>鼓励用道具主动修正机械传动。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>每条撞击链命中3种或以上不同标签的物品：+15分。</t>
+          <t>每次撞击结算命中3种或以上不同标签的物品：+15分。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>负价值物品完成结算后：额外+其负价值绝对值一半的分数，向下取整。每个物品每条链限1次。</t>
+          <t>负价值物品完成结算后：额外+其负价值绝对值一半的分数，向下取整。每个物品每次撞击结算限1次。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>相邻两个同标签物品中，一个被撞时：另一个+2分，每条链每个物品限1次。</t>
+          <t>相邻两个同标签物品中，一个被撞时：另一个+2分，每次撞击结算每个物品限1次。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>链结束时，若本局已经发生过污染结算、播种和大于等于5命中的撞击链：+45分，每局限1次。</t>
+          <t>本次撞击结算全部停止后时，若本局已经发生过污染结算、播种和大于等于5命中的撞击结算：+45分，每局限1次。</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>多目标道具；梦境钥匙；小水滴</t>
+          <t>多目标道具；梦值糖；小水滴</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
